--- a/courses/International-Corporate-Finance/projects/performance-ratios/models/templates/gaap-bridge-template.xlsx
+++ b/courses/International-Corporate-Finance/projects/performance-ratios/models/templates/gaap-bridge-template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,13 @@
       <color rgb="00999999"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Open Sans"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +101,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor rgb="FFFDE9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -189,6 +200,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -572,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -585,7 +601,7 @@
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="14" t="n"/>
       <c r="D4" s="5" t="n"/>
     </row>
     <row r="5">
@@ -594,7 +610,7 @@
           <t>Reporting Standard</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="14" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -608,7 +624,7 @@
           <t>IFRS Convergence Status</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="14" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -622,7 +638,7 @@
           <t>Conversion Tier Applied</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="14" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -636,7 +652,7 @@
           <t>Reporting Currency</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="14" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -650,7 +666,7 @@
           <t>Fiscal Year End</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="14" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -664,7 +680,7 @@
           <t>Source Document</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="14" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -678,9 +694,11 @@
           <t>Source URL</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="14" t="n"/>
       <c r="D11" s="5" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -729,10 +747,10 @@
           <t>Inventory Method (LIFO/FIFO)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="B17" s="6" t="inlineStr">
@@ -741,6 +759,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="n">
         <v>2</v>
@@ -750,10 +769,10 @@
           <t>Leases (IFRS 16 / VAS off-BS)</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="B20" s="6" t="inlineStr">
@@ -762,6 +781,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="8" t="n">
         <v>3</v>
@@ -771,10 +791,10 @@
           <t>R&amp;D / Development Costs</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="B23" s="6" t="inlineStr">
@@ -783,6 +803,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="8" t="n">
         <v>4</v>
@@ -792,10 +813,10 @@
           <t>Impairment Reversals</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="B26" s="6" t="inlineStr">
@@ -804,6 +825,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="8" t="n">
         <v>5</v>
@@ -813,10 +835,10 @@
           <t>Revenue Recognition Timing</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="B29" s="6" t="inlineStr">
@@ -825,6 +847,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -865,35 +889,37 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -942,10 +968,10 @@
           <t>EBITDA / EV/EBITDA</t>
         </is>
       </c>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
@@ -956,10 +982,10 @@
           <t>Current Ratio</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
@@ -970,10 +996,10 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
@@ -984,10 +1010,10 @@
           <t>Return on Assets (ROA)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
@@ -998,10 +1024,10 @@
           <t>Asset Turnover</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
@@ -1012,10 +1038,10 @@
           <t>Gross Margin</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
@@ -1026,10 +1052,10 @@
           <t>Inventory Turnover</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
@@ -1040,11 +1066,13 @@
           <t>Operating Income / EBIT</t>
         </is>
       </c>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-    </row>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+    </row>
+    <row r="49"/>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
@@ -1058,7 +1086,8 @@
           <t>Total adjustments identified</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="3" t="inlineStr">
@@ -1066,7 +1095,8 @@
           <t>Adjustments quantified</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="3" t="inlineStr">
@@ -1074,7 +1104,8 @@
           <t>Adjustments noted but not quantified</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="3" t="inlineStr">
@@ -1082,7 +1113,8 @@
           <t>Overall impact on comparability</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="5" t="n"/>
       <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Low / Medium / High</t>
@@ -1095,7 +1127,8 @@
           <t>Analyst name</t>
         </is>
       </c>
-      <c r="C56" s="4" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="3" t="inlineStr">
@@ -1103,8 +1136,11 @@
           <t>Date completed</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
-    </row>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
